--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66988408</v>
+        <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99120</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +797,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rissna, vägkant 1,5 km SSO om vägkorset i byn, Jmt</t>
+          <t>Rissna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517731</v>
+        <v>517713</v>
       </c>
       <c r="R3" t="n">
-        <v>6990925</v>
+        <v>6990949</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,37 +869,38 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Atlasinventering och läger i Jämtland</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66988408</t>
+          <t>https://artportalen.se/Sighting/136956312</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66988423</v>
+        <v>66988408</v>
       </c>
       <c r="B4" t="n">
-        <v>99142</v>
+        <v>99120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -992,16 +997,16 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66988423</t>
+          <t>https://artportalen.se/Sighting/66988408</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66988420</v>
+        <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>100143</v>
+        <v>99355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,37 +1014,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222467</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rissna, vägkant 1,5 km SSO om vägkorset i byn, Jmt</t>
+          <t>Rissna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517731</v>
+        <v>517711</v>
       </c>
       <c r="R5" t="n">
-        <v>6990925</v>
+        <v>6990954</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,12 +1072,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,26 +1086,572 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136956304</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136956308</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99355</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rissna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>517704</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6990945</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136956308</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>66988423</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rissna, vägkant 1,5 km SSO om vägkorset i byn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>517731</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6990925</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-08-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-08-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Staffan Åström</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Staffan Åström</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66988423</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136956310</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rissna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>517712</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6990951</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136956310</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136956300</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102705</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rissna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>517708</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6990954</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136956300</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>66988420</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100143</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rissna, vägkant 1,5 km SSO om vägkorset i byn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>517731</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6990925</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-08-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-08-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Atlasinventering och läger i Jämtland</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/66988420</t>
         </is>
@@ -1108,6 +1663,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36591-2026 artfynd.xlsx
+++ b/artfynd/A 36591-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956312</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136956304</v>
       </c>
       <c r="B5" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136956308</v>
       </c>
       <c r="B6" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136956310</v>
       </c>
       <c r="B8" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136956300</v>
       </c>
       <c r="B9" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
